--- a/data/trending_integrated_20260907_12.xlsx
+++ b/data/trending_integrated_20260907_12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,70 +563,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>두산퓨얼셀</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51800</v>
+        <v>30550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+18.13%</t>
+          <t>+30.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>160</v>
+        <v>798</v>
       </c>
       <c r="F2" t="n">
-        <v>106</v>
+        <v>313</v>
       </c>
       <c r="G2" t="n">
-        <v>568</v>
+        <v>1160</v>
       </c>
       <c r="H2" t="n">
-        <v>14.18</v>
+        <v>0.16</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>43850</v>
+        <v>23500</v>
       </c>
       <c r="K2" t="n">
-        <v>45650</v>
+        <v>23200</v>
       </c>
       <c r="L2" t="n">
-        <v>55000</v>
+        <v>30550</v>
       </c>
       <c r="M2" t="n">
-        <v>45650</v>
+        <v>22800</v>
       </c>
       <c r="N2" t="n">
-        <v>13.71</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>129586984575</v>
+        <v>775414311525</v>
       </c>
       <c r="P2" t="n">
-        <v>108900</v>
+        <v>30550</v>
       </c>
       <c r="Q2" t="n">
-        <v>18230</v>
+        <v>8200</v>
       </c>
       <c r="R2" t="n">
-        <v>176000</v>
+        <v>-9000</v>
       </c>
       <c r="S2" t="n">
-        <v>44000</v>
+        <v>-1000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 기대감 및 6~7만원 구간 매물벽 약세 전망. 단기 급등 후 소강 상태 진입 및 4만원 재진입 가능성 언급. 공급 계약 발표 후 급등 사례 언급.</t>
+          <t>주포 등장 및 거래량 증가 언급. 3만원 돌파 및 상한가 기대감 높으나, 주가 조작 의혹 및 단기 급등 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,11 +635,11 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', '매물벽', '공급계약']</t>
+          <t>['주포', '거래량', '상한가']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>336260</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27600</v>
+        <v>10320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+17.45%</t>
+          <t>+23.59%</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E3" t="n">
+        <v>103</v>
+      </c>
+      <c r="F3" t="n">
+        <v>73</v>
+      </c>
+      <c r="G3" t="n">
+        <v>133</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>8350</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8660</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10850</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8420</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O3" t="n">
+        <v>112187227720</v>
+      </c>
+      <c r="P3" t="n">
+        <v>20850</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4020</v>
+      </c>
+      <c r="R3" t="n">
+        <v>70000</v>
+      </c>
+      <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>649</v>
-      </c>
-      <c r="F3" t="n">
-        <v>271</v>
-      </c>
-      <c r="G3" t="n">
-        <v>951</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>23500</v>
-      </c>
-      <c r="K3" t="n">
-        <v>23200</v>
-      </c>
-      <c r="L3" t="n">
-        <v>29600</v>
-      </c>
-      <c r="M3" t="n">
-        <v>22800</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>665867321400</v>
-      </c>
-      <c r="P3" t="n">
-        <v>29600</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>8200</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-9000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-1000</v>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 확인 및 거래량 증가에 따른 상승 기대감. 주포의 움직임 및 종가 상한가 가능성 언급. '세계 1위, 최초' 등의 수식어 활용.</t>
+          <t>두산에너빌리티 연관된 가스터빈 테마 및 일론 머스크 xAI 관련 뉴스 언급. 스카이랩스 다음 테마로 지목되나, 주가 조작 및 재료 소멸 우려도 공존.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['CART 혈압계', '거래량', '주포']</t>
+          <t>['가스터빈', '테마', '주가조작']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6430</v>
+        <v>10000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+9.91%</t>
+          <t>+22.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.7</v>
+        <v>0.44</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="H4" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5850</v>
+        <v>8180</v>
       </c>
       <c r="K4" t="n">
-        <v>6000</v>
+        <v>8200</v>
       </c>
       <c r="L4" t="n">
-        <v>6525</v>
+        <v>10390</v>
       </c>
       <c r="M4" t="n">
-        <v>5940</v>
+        <v>8120</v>
       </c>
       <c r="N4" t="n">
-        <v>2.31</v>
+        <v>1.14</v>
       </c>
       <c r="O4" t="n">
-        <v>13532531285</v>
+        <v>68519688910</v>
       </c>
       <c r="P4" t="n">
-        <v>21500</v>
+        <v>22500</v>
       </c>
       <c r="Q4" t="n">
-        <v>2300</v>
+        <v>4560</v>
       </c>
       <c r="R4" t="n">
-        <v>-14000</v>
+        <v>110000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>임상 2a의 의미 및 신약 개발 가능성 언급. 현대바이오와의 연관성 및 유증 자금 활용 가능성. '게임 체인저' 가능성 제시 및 저가 매수 권유.</t>
+          <t>AI 관련주로 스카이랩스와 비교하며 상승 기대감. 프로그램 매수 등장 및 9300원 돌파 시 VI 언급. 무빙에 대한 불안감도 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['임상 2a', '신약 개발', '게임 체인저']</t>
+          <t>['AI', '프로그램매수', 'VI']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>0039P0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3575</v>
+        <v>51200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+9.49%</t>
+          <t>+16.76%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.52</v>
+        <v>0.47</v>
       </c>
       <c r="E5" t="n">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="G5" t="n">
-        <v>206</v>
+        <v>590</v>
       </c>
       <c r="H5" t="n">
-        <v>1.25</v>
+        <v>14.18</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3265</v>
+        <v>43850</v>
       </c>
       <c r="K5" t="n">
-        <v>3200</v>
+        <v>45650</v>
       </c>
       <c r="L5" t="n">
-        <v>3900</v>
+        <v>55000</v>
       </c>
       <c r="M5" t="n">
-        <v>3185</v>
+        <v>45650</v>
       </c>
       <c r="N5" t="n">
-        <v>1.77</v>
+        <v>13.71</v>
       </c>
       <c r="O5" t="n">
-        <v>166454174974</v>
+        <v>137885511075</v>
       </c>
       <c r="P5" t="n">
-        <v>3900</v>
+        <v>108900</v>
       </c>
       <c r="Q5" t="n">
-        <v>1246</v>
+        <v>18230</v>
       </c>
       <c r="R5" t="n">
-        <v>-25000</v>
+        <v>176000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>단기적인 상승 및 하락 반복, 투자 주의 필요성 언급. 탈모 관련 사업 우려 및 회사의 재무 상태에 대한 부정적 시각. 프로그램 매매 활용 후 이탈 가능성 시사.</t>
+          <t>공매도 감소 및 기술적 반등 기대감. 9월 2일 수주 공시 확인되었으나, 단기 급등 후 조정 가능성도 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['투자주의', '탈모', '프로그램 매매']</t>
+          <t>['공매도', '수주', '저항']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>215500</v>
+        <v>18340</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+6.95%</t>
+          <t>+16.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>404</v>
+        <v>116</v>
       </c>
       <c r="F6" t="n">
-        <v>220</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>1127</v>
+        <v>105</v>
       </c>
       <c r="H6" t="n">
-        <v>29.46</v>
+        <v>1.08</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>201500</v>
+        <v>15750</v>
       </c>
       <c r="K6" t="n">
-        <v>212500</v>
+        <v>16080</v>
       </c>
       <c r="L6" t="n">
-        <v>225500</v>
+        <v>18900</v>
       </c>
       <c r="M6" t="n">
-        <v>212500</v>
+        <v>15920</v>
       </c>
       <c r="N6" t="n">
-        <v>29.51</v>
+        <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>284539442750</v>
+        <v>66770388500</v>
       </c>
       <c r="P6" t="n">
-        <v>438000</v>
+        <v>34650</v>
       </c>
       <c r="Q6" t="n">
-        <v>74700</v>
+        <v>6980</v>
       </c>
       <c r="R6" t="n">
-        <v>353000</v>
+        <v>-21000</v>
       </c>
       <c r="S6" t="n">
-        <v>124000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>로봇 사업 관련 기술력 부각 및 60년 기술 노하우 강조. 외인·기관 매수세 유입에 따른 상승 기대감 표출.</t>
+          <t>18500원 돌파 및 저평가 기업 주장. 반도체 주 흐름 연관 기대감 있으나, 투매 및 음봉 전환 가능성도 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['로봇', '기술력', '액츄에이터']</t>
+          <t>['저평가', '저항대', '투매']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>387690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1747000</v>
+        <v>3640</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.07%</t>
+          <t>+11.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.52</v>
       </c>
       <c r="E7" t="n">
-        <v>794</v>
+        <v>123</v>
       </c>
       <c r="F7" t="n">
-        <v>419</v>
+        <v>77</v>
       </c>
       <c r="G7" t="n">
-        <v>2127</v>
+        <v>219</v>
       </c>
       <c r="H7" t="n">
-        <v>50.5</v>
+        <v>1.25</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1647000</v>
+        <v>3265</v>
       </c>
       <c r="K7" t="n">
-        <v>1737000</v>
+        <v>3200</v>
       </c>
       <c r="L7" t="n">
-        <v>1751000</v>
+        <v>3900</v>
       </c>
       <c r="M7" t="n">
-        <v>1733000</v>
+        <v>3185</v>
       </c>
       <c r="N7" t="n">
-        <v>50.45</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>2682641606500</v>
+        <v>181284511786</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>3900</v>
       </c>
       <c r="Q7" t="n">
-        <v>274000</v>
+        <v>1246</v>
       </c>
       <c r="R7" t="n">
-        <v>330000</v>
+        <v>-25000</v>
       </c>
       <c r="S7" t="n">
-        <v>138000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외국인 및 기관 쌍끌이 매수세 유입에 따른 상승 추세 가속화 전망. 자사주 매입 기대감 및 메모리 재고 부족 뉴스 언급. 200만원 터치 및 급등 가능성 제시.</t>
+          <t>단기적인 상승 및 하락 반복, 투자 주의 필요성 언급. 탈모 관련 사업 우려 및 회사의 재무 상태에 대한 부정적 시각. 프로그램 매매 활용 후 이탈 가능성 시사.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['자사주매입', '메모리 재고', '쌍끌이 매수']</t>
+          <t>['투자주의', '탈모', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83650</v>
+        <v>87000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.62%</t>
+          <t>+9.85%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="F8" t="n">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="G8" t="n">
-        <v>508</v>
+        <v>851</v>
       </c>
       <c r="H8" t="n">
         <v>23.53</v>
@@ -1153,7 +1153,7 @@
         <v>80200</v>
       </c>
       <c r="L8" t="n">
-        <v>84700</v>
+        <v>87300</v>
       </c>
       <c r="M8" t="n">
         <v>79000</v>
@@ -1162,7 +1162,7 @@
         <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>170941399250</v>
+        <v>265912925200</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대규모 가스복합화력발전 투자 확정 및 하반기 본격 수주 기대감. 기술력 입증 및 10만원 돌파 전망. 원전주 전반적인 상승세 속에서 상대적 우위 확인.</t>
+          <t>일론 머스크 xAI와의 협력 소식에 따른 기대감 상승. 대규모 투자 및 가스터빈 기술력 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['대미투자', '가스터빈', '본격수주']</t>
+          <t>['복합화력발전', '가스터빈', '투자']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,123 +1207,123 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8350</v>
+        <v>6340</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.03%</t>
+          <t>+8.38%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>142</v>
+        <v>465</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>1.61</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7950</v>
+        <v>5850</v>
       </c>
       <c r="K9" t="n">
-        <v>8200</v>
+        <v>6000</v>
       </c>
       <c r="L9" t="n">
-        <v>9210</v>
+        <v>6550</v>
       </c>
       <c r="M9" t="n">
-        <v>7980</v>
+        <v>5940</v>
       </c>
       <c r="N9" t="n">
-        <v>1.32</v>
+        <v>2.31</v>
       </c>
       <c r="O9" t="n">
-        <v>88855097300</v>
+        <v>14730918325</v>
       </c>
       <c r="P9" t="n">
-        <v>15960</v>
+        <v>21500</v>
       </c>
       <c r="Q9" t="n">
-        <v>3500</v>
+        <v>2300</v>
       </c>
       <c r="R9" t="n">
-        <v>149000</v>
+        <v>-14000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
+          <t>임상 2a 및 WCLC 2026 관련 호재 언급. 6500원 돌파 시 기대감 고조. 현대바이오와 비교하며 게임 체인저 가능성 주장. 인내심 필요 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['미프진', '거래량', '수급']</t>
+          <t>['임상', '신약', '게임체인저']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17640</v>
+        <v>215500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.69%</t>
+          <t>+6.95%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>442</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>242</v>
       </c>
       <c r="G10" t="n">
-        <v>146</v>
+        <v>1247</v>
       </c>
       <c r="H10" t="n">
-        <v>10.4</v>
+        <v>29.46</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16850</v>
+        <v>201500</v>
       </c>
       <c r="K10" t="n">
-        <v>16870</v>
+        <v>212500</v>
       </c>
       <c r="L10" t="n">
-        <v>17800</v>
+        <v>225500</v>
       </c>
       <c r="M10" t="n">
-        <v>16590</v>
+        <v>212500</v>
       </c>
       <c r="N10" t="n">
-        <v>10.36</v>
+        <v>29.51</v>
       </c>
       <c r="O10" t="n">
-        <v>77896447200</v>
+        <v>295660731750</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>438000</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>74700</v>
       </c>
       <c r="R10" t="n">
-        <v>266000</v>
+        <v>353000</v>
       </c>
       <c r="S10" t="n">
-        <v>58000</v>
+        <v>124000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
+          <t>LG전자, 프로그램 매수세 유입 및 60년 모터 기술 기반 로봇 사업 기대감으로 급등. 젠슨 황 부재 속 목표 주가 100만원 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['러우전쟁', '건설주', '종전']</t>
+          <t>['로봇', 'CES 2026', '모터 기술']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>265750</v>
+        <v>1750000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.01%</t>
+          <t>+6.25%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="F11" t="n">
-        <v>449</v>
+        <v>413</v>
       </c>
       <c r="G11" t="n">
-        <v>1870</v>
+        <v>2333</v>
       </c>
       <c r="H11" t="n">
-        <v>46.73</v>
+        <v>50.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>255500</v>
+        <v>1647000</v>
       </c>
       <c r="K11" t="n">
-        <v>267000</v>
+        <v>1737000</v>
       </c>
       <c r="L11" t="n">
-        <v>268000</v>
+        <v>1751000</v>
       </c>
       <c r="M11" t="n">
-        <v>264000</v>
+        <v>1733000</v>
       </c>
       <c r="N11" t="n">
-        <v>46.71</v>
+        <v>50.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1845746056250</v>
+        <v>3195968376500</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>69600</v>
+        <v>274000</v>
       </c>
       <c r="R11" t="n">
-        <v>1189000</v>
+        <v>330000</v>
       </c>
       <c r="S11" t="n">
-        <v>911000</v>
+        <v>138000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 유입에도 불구하고, 정치적 이슈 및 보수적인 시장 전망. 반도체 관련 긍정적 뉴스에도 불구하고 개인 물량 털어내기 및 음전 가능성 언급.</t>
+          <t>개인 매도세 속 외인·기관 쌍끌이 매수 확인. 메모리 재고 소진 및 상승 추세 가속 기대. 200만원 목표 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '외국인 매수', '기관 매수']</t>
+          <t>['메모리', '수급', '추세']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13460</v>
+        <v>17780</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.46%</t>
+          <t>+5.52%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>285</v>
+        <v>167</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82</v>
+        <v>10.4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13010</v>
+        <v>16850</v>
       </c>
       <c r="K12" t="n">
-        <v>13420</v>
+        <v>16870</v>
       </c>
       <c r="L12" t="n">
-        <v>14100</v>
+        <v>17800</v>
       </c>
       <c r="M12" t="n">
-        <v>13410</v>
+        <v>16590</v>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>63876292275</v>
+        <v>85328950395</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>1252</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>317000</v>
+        <v>266000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>광통신 섹터 강세 및 공매도 물량 소화 기대. 14000원 물린 개미.</t>
+          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '공매도', '섹터']</t>
+          <t>['러우전쟁', '건설주', '종전']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6880</v>
+        <v>8370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+2.53%</t>
+          <t>+5.28%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.85</v>
+        <v>-0.72</v>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="H13" t="n">
-        <v>16.4</v>
+        <v>0.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6710</v>
+        <v>7950</v>
       </c>
       <c r="K13" t="n">
-        <v>6680</v>
+        <v>8200</v>
       </c>
       <c r="L13" t="n">
-        <v>7040</v>
+        <v>9210</v>
       </c>
       <c r="M13" t="n">
-        <v>6600</v>
+        <v>7980</v>
       </c>
       <c r="N13" t="n">
-        <v>15.55</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>9747060585</v>
+        <v>92892003420</v>
       </c>
       <c r="P13" t="n">
-        <v>13000</v>
+        <v>15960</v>
       </c>
       <c r="Q13" t="n">
-        <v>6030</v>
+        <v>3500</v>
       </c>
       <c r="R13" t="n">
-        <v>33000</v>
+        <v>149000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>한화 세미텍, 한화 로보틱스 IPO 언급 및 반도체, 로봇 사업 관련 기대감. 하지만 일부 매도 움직임 관찰.</t>
+          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['IPO', '반도체', '로봇']</t>
+          <t>['미프진', '거래량', '수급']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,169 +1660,169 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22600</v>
+        <v>267000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+4.50%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.62</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>784</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>428</v>
       </c>
       <c r="G14" t="n">
-        <v>130</v>
+        <v>1802</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6</v>
+        <v>46.73</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>22500</v>
+        <v>255500</v>
       </c>
       <c r="K14" t="n">
-        <v>23100</v>
+        <v>267000</v>
       </c>
       <c r="L14" t="n">
-        <v>24000</v>
+        <v>268000</v>
       </c>
       <c r="M14" t="n">
-        <v>21500</v>
+        <v>264000</v>
       </c>
       <c r="N14" t="n">
-        <v>4.98</v>
+        <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>121946555900</v>
+        <v>2143200430750</v>
       </c>
       <c r="P14" t="n">
-        <v>50600</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>9070</v>
+        <v>69600</v>
       </c>
       <c r="R14" t="n">
-        <v>28000</v>
+        <v>1189000</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>911000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
+          <t>외국인 및 기관 매수세 유입, 재고 바닥 및 3분기 영업이익 120조 예상 언급. 단, 정치적 발언 및 감정적 기대 포함.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '2연상']</t>
+          <t>['영업이익', '수급', '전망']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30200</v>
+        <v>13490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+3.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.4</v>
+        <v>-0.09</v>
       </c>
       <c r="E15" t="n">
+        <v>69</v>
+      </c>
+      <c r="F15" t="n">
         <v>46</v>
       </c>
-      <c r="F15" t="n">
-        <v>29</v>
-      </c>
       <c r="G15" t="n">
-        <v>76</v>
+        <v>347</v>
       </c>
       <c r="H15" t="n">
-        <v>48.96</v>
+        <v>1.82</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>30200</v>
+        <v>13010</v>
       </c>
       <c r="K15" t="n">
-        <v>30350</v>
+        <v>13420</v>
       </c>
       <c r="L15" t="n">
-        <v>30900</v>
+        <v>14100</v>
       </c>
       <c r="M15" t="n">
-        <v>29900</v>
+        <v>13400</v>
       </c>
       <c r="N15" t="n">
-        <v>24.02</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>61997678325</v>
+        <v>67858985950</v>
       </c>
       <c r="P15" t="n">
-        <v>31200</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>21000</v>
+        <v>1252</v>
       </c>
       <c r="R15" t="n">
-        <v>222000</v>
+        <v>317000</v>
       </c>
       <c r="S15" t="n">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>광통신 섹터 강세 및 공매도 물량 소화 기대. 14000원 물린 개미.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['광통신', '공매도', '섹터']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15970</v>
+        <v>6750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>+0.60%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>392</v>
+        <v>94</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16090</v>
+        <v>6710</v>
       </c>
       <c r="K16" t="n">
-        <v>16150</v>
+        <v>6680</v>
       </c>
       <c r="L16" t="n">
-        <v>16480</v>
+        <v>7040</v>
       </c>
       <c r="M16" t="n">
-        <v>15830</v>
+        <v>6600</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>15.55</v>
       </c>
       <c r="O16" t="n">
-        <v>33394293660</v>
+        <v>10812466265</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>13000</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>6030</v>
       </c>
       <c r="R16" t="n">
-        <v>-21000</v>
+        <v>33000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>17000선 지지 여부 불확실성 및 개인 간의 치열한 눈치 싸움. 반도체 관련 긍정적 뉴스에도 불구하고 '개잡주' 언급 및 실적 분석 필요성 제기.</t>
+          <t>한화머시너리앤서비스홀딩스, 공매도 압박 및 IPO 관련 불확실성 언급. 로봇 및 반도체 사업에 대한 기대감과 우려 혼재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['반도체', '주포', '2분기보고서']</t>
+          <t>['공매도', 'IPO', '로봇']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,130 +1936,130 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10140</v>
+        <v>16100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
-        <v>162</v>
+        <v>450</v>
       </c>
       <c r="H17" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10390</v>
+        <v>16090</v>
       </c>
       <c r="K17" t="n">
-        <v>10050</v>
+        <v>16150</v>
       </c>
       <c r="L17" t="n">
-        <v>11000</v>
+        <v>16480</v>
       </c>
       <c r="M17" t="n">
-        <v>9770</v>
+        <v>15830</v>
       </c>
       <c r="N17" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>18367413380</v>
+        <v>36134113480</v>
       </c>
       <c r="P17" t="n">
-        <v>15640</v>
+        <v>19380</v>
       </c>
       <c r="Q17" t="n">
-        <v>5470</v>
+        <v>3200</v>
       </c>
       <c r="R17" t="n">
-        <v>-85000</v>
+        <v>-21000</v>
       </c>
       <c r="S17" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>급등 기대감 및 2백만원 목표가 제시. 공매도 소굴이라는 부정적 의견과 함께 매집 및 순환매 기대. 금일 12층 목표.</t>
+          <t>메가특구법 발의 및 호남 반도체 산단 관련 기대감. 반도체 첫 삽 시 15만원 목표 언급 있으나, 구체적 근거는 부족.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['급등', '공매도', '순환매']</t>
+          <t>['반도체', '산단', '인프라']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5500</v>
+        <v>22500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.18%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E18" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
         <v>49</v>
       </c>
       <c r="G18" t="n">
-        <v>212</v>
+        <v>154</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,130 +2067,130 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>5740</v>
+        <v>22500</v>
       </c>
       <c r="K18" t="n">
-        <v>5250</v>
+        <v>23100</v>
       </c>
       <c r="L18" t="n">
-        <v>5530</v>
+        <v>24000</v>
       </c>
       <c r="M18" t="n">
-        <v>5000</v>
+        <v>21500</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O18" t="n">
-        <v>3099343510</v>
+        <v>126039557675</v>
       </c>
       <c r="P18" t="n">
-        <v>9680</v>
+        <v>50600</v>
       </c>
       <c r="Q18" t="n">
-        <v>371</v>
+        <v>9070</v>
       </c>
       <c r="R18" t="n">
-        <v>-9000</v>
+        <v>28000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 악재 뉴스 발생으로 인한 하한가 우려. 투심 훼손 및 구주 매각 관련 불확실성. 'ㅈ되었다', '탈출' 등 부정적 심리 표현.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재 뉴스', '투심 훼손']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>아난티</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5470</v>
+        <v>30200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.20%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="H19" t="n">
-        <v>4.81</v>
+        <v>48.95</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5710</v>
+        <v>30200</v>
       </c>
       <c r="K19" t="n">
-        <v>5640</v>
+        <v>30350</v>
       </c>
       <c r="L19" t="n">
-        <v>5650</v>
+        <v>30900</v>
       </c>
       <c r="M19" t="n">
-        <v>5270</v>
+        <v>29900</v>
       </c>
       <c r="N19" t="n">
-        <v>4.39</v>
+        <v>24.02</v>
       </c>
       <c r="O19" t="n">
-        <v>15592118200</v>
+        <v>66912181025</v>
       </c>
       <c r="P19" t="n">
-        <v>10480</v>
+        <v>31200</v>
       </c>
       <c r="Q19" t="n">
-        <v>3150</v>
+        <v>21000</v>
       </c>
       <c r="R19" t="n">
-        <v>-336000</v>
+        <v>222000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>시진핑 방미 관련 뉴스 부재 및 하락 시작 우려. 대북주 변동성 및 주가 조작 의혹 제기. 외국인, 연기금 매수세 일부 확인.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['시진핑', '대북주', '주가 조작']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,7 +2212,283 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
+          <t>003490</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>바이오니아</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>10120</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-2.60%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E20" t="n">
+        <v>65</v>
+      </c>
+      <c r="F20" t="n">
+        <v>44</v>
+      </c>
+      <c r="G20" t="n">
+        <v>180</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>10390</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10050</v>
+      </c>
+      <c r="L20" t="n">
+        <v>11000</v>
+      </c>
+      <c r="M20" t="n">
+        <v>9770</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>18805893680</v>
+      </c>
+      <c r="P20" t="n">
+        <v>15640</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5470</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-85000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>급등 기대감 및 2백만원 목표가 제시. 공매도 소굴이라는 부정적 의견과 함께 매집 및 순환매 기대. 금일 12층 목표.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['급등', '공매도', '순환매']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>064550</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>아난티</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5450</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-4.55%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E21" t="n">
+        <v>69</v>
+      </c>
+      <c r="F21" t="n">
+        <v>48</v>
+      </c>
+      <c r="G21" t="n">
+        <v>203</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>5710</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5640</v>
+      </c>
+      <c r="L21" t="n">
+        <v>5650</v>
+      </c>
+      <c r="M21" t="n">
+        <v>5270</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O21" t="n">
+        <v>16425603565</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10480</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3150</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-336000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>시진핑 방미 관련 뉴스 부재 및 하락 시작 우려. 대북주 변동성 및 주가 조작 의혹 제기. 외국인, 연기금 매수세 일부 확인.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['시진핑', '대북주', '주가 조작']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>025980</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5370</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-6.45%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>93</v>
+      </c>
+      <c r="F22" t="n">
+        <v>51</v>
+      </c>
+      <c r="G22" t="n">
+        <v>229</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5530</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3565711900</v>
+      </c>
+      <c r="P22" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>371</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 및 구주 매각 관련 악재 뉴스가 연이어 발생하며 하한가 우려가 제기되었으나, 일부에서는 보합 가능성 및 악재 노출 완료 언급.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재', '매각']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>226340</t>
         </is>
       </c>
     </row>
